--- a/data/npc_unlocks.xlsx
+++ b/data/npc_unlocks.xlsx
@@ -1,34 +1,136 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/68dca1814c1352fc/Documents/hilling-game/data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="19" documentId="11_AA50D487516364CFEB3B98154B381EBAB674E3DB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8A5AFC0D-3CAD-4C04-AAF3-F560F2670C46}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="18330" yWindow="5445" windowWidth="17970" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="npc_unlocks" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="npc_unlocks" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="26">
+  <si>
+    <t>threshold</t>
+  </si>
+  <si>
+    <t>npc_id</t>
+  </si>
+  <si>
+    <t>display_name</t>
+  </si>
+  <si>
+    <t>role</t>
+  </si>
+  <si>
+    <t>unlocks</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>y</t>
+  </si>
+  <si>
+    <t>note</t>
+  </si>
+  <si>
+    <t>unique</t>
+  </si>
+  <si>
+    <t>weapon_upgrade</t>
+  </si>
+  <si>
+    <t>무기 제작/강화 해금</t>
+  </si>
+  <si>
+    <t>placeable</t>
+  </si>
+  <si>
+    <t>serving</t>
+  </si>
+  <si>
+    <t>서빙 보조 배치 가능</t>
+  </si>
+  <si>
+    <t>kitchen</t>
+  </si>
+  <si>
+    <t>주방 보조 배치 가능</t>
+  </si>
+  <si>
+    <t>new_region</t>
+  </si>
+  <si>
+    <t>새 탐사 지역 해금</t>
+  </si>
+  <si>
+    <t>카터</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>carter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>리암</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>camila</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>liam</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>카밀라</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>엠마</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>emma</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <name val="Calibri"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -47,81 +149,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -408,175 +455,149 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
+    <col min="1" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>threshold</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>npc_id</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>display_name</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>role</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>unlocks</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2">
         <v>100</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>hana</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>하나</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>unique</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>weapon_upgrade</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>무기 제작/강화 해금</t>
-        </is>
+      <c r="B2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2">
+        <v>0.31</v>
+      </c>
+      <c r="G2">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="H2" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3">
         <v>250</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>seorin</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>서린</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>placeable</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>serving</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>서빙 보조 배치 가능</t>
-        </is>
+      <c r="B3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3">
+        <v>0.64</v>
+      </c>
+      <c r="G3">
+        <v>0.45</v>
+      </c>
+      <c r="H3" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4">
         <v>450</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>murim</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>무림</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>placeable</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>kitchen</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>주방 보조 배치 가능</t>
-        </is>
+      <c r="B4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4">
+        <v>0.74</v>
+      </c>
+      <c r="G4">
+        <v>0.72</v>
+      </c>
+      <c r="H4" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5">
         <v>700</v>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>dain</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>다인</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>unique</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>new_region</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>새 탐사 지역 해금</t>
-        </is>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5">
+        <v>0.2</v>
+      </c>
+      <c r="G5">
+        <v>0.82</v>
+      </c>
+      <c r="H5" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/npc_unlocks.xlsx
+++ b/data/npc_unlocks.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/68dca1814c1352fc/Documents/hilling-game/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="11_AA50D487516364CFEB3B98154B381EBAB674E3DB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8A5AFC0D-3CAD-4C04-AAF3-F560F2670C46}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="11_AA50D487516364CFEB3B98154B381EBAB674E3DB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{06DEE403-3608-42AC-A56B-B6C199CEC84C}"/>
   <bookViews>
-    <workbookView xWindow="18330" yWindow="5445" windowWidth="17970" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="22635" windowHeight="18480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="npc_unlocks" sheetId="1" r:id="rId1"/>
@@ -165,10 +165,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -520,7 +516,7 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
@@ -546,7 +542,7 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>450</v>
+        <v>650</v>
       </c>
       <c r="B4" t="s">
         <v>25</v>
@@ -572,7 +568,7 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
